--- a/ig/DM-SIDOBA/CodeSystem-tre-r424-qualification-orientation.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r424-qualification-orientation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>Property</t>
   </si>
@@ -208,7 +208,15 @@
     <t>Cible</t>
   </si>
   <si>
+    <t>Qualification d'une décision basée uniquement sur les attentes et les besoins évalués de la personne et considérée par l'équipe pluridisciplinaire ou la CDAPH comme la réponse la plus adaptée à ces attentes et besoins sans prendre en compte la réalité de l'offre disponible.
+L'orientation cible est aussi appelée "orientation hors contrainte de l’offre, théorique ou idéale".</t>
+  </si>
+  <si>
     <t>Alternative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'orientation alternative est partiellement adaptée au regard des attentes et des besoins évalués de la personne. Elle prend bien en compte la réalité de l'offre disponible. Elle a ainsi plus de chance d'être mise en œuvre.
+L'orientation alternative est aussi appelée "Orientation par défaut". </t>
   </si>
 </sst>
 </file>
@@ -653,7 +661,9 @@
       <c r="C2" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -663,9 +673,11 @@
         <v>35</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
